--- a/Data_Uji.xlsx
+++ b/Data_Uji.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\proyek-spk\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\proyek-spk\SI-PEKA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6ECC2FF8-0A1F-470C-A6D5-4D328DD2ABBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98CB589-5FEA-4DF1-909B-77A5AF1459E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{ADFE4CBF-4B52-4ADF-81C6-E795E7ECF4BD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t>NO</t>
   </si>
@@ -74,54 +74,36 @@
     <t>DATA PENGUJIAN</t>
   </si>
   <si>
-    <t>DEPOT TIRTA MAKMUR</t>
-  </si>
-  <si>
     <t>7.2</t>
   </si>
   <si>
     <t>0.5</t>
   </si>
   <si>
-    <t>DEPOT SUMBER ALAM</t>
-  </si>
-  <si>
     <t>6.2</t>
   </si>
   <si>
     <t>1.1</t>
   </si>
   <si>
-    <t>DEPOT BENING HATI</t>
-  </si>
-  <si>
     <t>7.4</t>
   </si>
   <si>
     <t>0.8</t>
   </si>
   <si>
-    <t>DEPOT AIR SEJUK</t>
-  </si>
-  <si>
     <t>8.0</t>
   </si>
   <si>
     <t>3.5</t>
   </si>
   <si>
-    <t>DEPOT KAPUAS JAYA</t>
-  </si>
-  <si>
     <t>7.1</t>
   </si>
   <si>
     <t>2.8</t>
   </si>
   <si>
-    <t>DEPOT AQUA PONTI</t>
-  </si>
-  <si>
     <t>8.8</t>
   </si>
   <si>
@@ -134,9 +116,6 @@
     <t>0.1</t>
   </si>
   <si>
-    <t>DEPOT BINTANG</t>
-  </si>
-  <si>
     <t>7.0</t>
   </si>
   <si>
@@ -146,18 +125,12 @@
     <t>5.5</t>
   </si>
   <si>
-    <t>DEPOT TIRTA BORNEO</t>
-  </si>
-  <si>
     <t>7.6</t>
   </si>
   <si>
     <t>1.2</t>
   </si>
   <si>
-    <t>DEPOT ALAM SUTERA</t>
-  </si>
-  <si>
     <t>6.0</t>
   </si>
   <si>
@@ -171,9 +144,6 @@
   </si>
   <si>
     <t>2.9</t>
-  </si>
-  <si>
-    <t>DEPOT ZONA AIR</t>
   </si>
   <si>
     <t>4.8</t>
@@ -230,13 +200,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -250,6 +217,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -592,293 +563,273 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>7</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="2">
+        <v>110</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="2">
+        <v>45</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="2">
+        <v>315</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>6</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="2">
+        <v>150</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
         <v>7</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="B11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="2">
+        <v>280</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="3">
-        <v>2</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="B12" s="4"/>
+      <c r="C12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="2">
+        <v>90</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
         <v>9</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="B13" s="4"/>
+      <c r="C13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="2">
+        <v>15</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
         <v>10</v>
       </c>
-      <c r="D6" s="3">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="3">
-        <v>3</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="B14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="2">
+        <v>5</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
+        <v>11</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="2">
+        <v>420</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
         <v>12</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="B16" s="4"/>
+      <c r="C16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="2">
+        <v>135</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
         <v>13</v>
       </c>
-      <c r="D7" s="3">
-        <v>110</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="3">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="3">
-        <v>45</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
-        <v>5</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="3">
-        <v>315</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="3">
-        <v>150</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="3">
-        <v>7</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="B17" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="2">
         <v>25</v>
       </c>
-      <c r="D11" s="3">
-        <v>280</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="3">
-        <v>8</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="3">
-        <v>90</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="3">
-        <v>9</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="3">
-        <v>15</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="3">
-        <v>10</v>
-      </c>
-      <c r="B14" s="5" t="s">
+      <c r="E17" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="3">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="3">
-        <v>11</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="3">
-        <v>420</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="3">
-        <v>12</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="3">
-        <v>135</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="3">
-        <v>13</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="3">
-        <v>25</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>14</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>42</v>
-      </c>
+      <c r="B18" s="7"/>
       <c r="C18" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D18" s="1">
         <v>290</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>15</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>45</v>
-      </c>
+      <c r="B19" s="5"/>
       <c r="C19" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D19" s="1">
         <v>550</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
